--- a/sheets/fig3.xlsx
+++ b/sheets/fig3.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Neu" sheetId="1" state="visible" r:id="rId3"/>
@@ -2487,14 +2487,14 @@
     <xdr:from>
       <xdr:col>36</xdr:col>
       <xdr:colOff>93240</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>177120</xdr:rowOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>15480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>39</xdr:col>
-      <xdr:colOff>288360</xdr:colOff>
+      <xdr:colOff>288000</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>94320</xdr:rowOff>
+      <xdr:rowOff>113400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2503,8 +2503,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18894240" y="928440"/>
-          <a:ext cx="2399400" cy="279000"/>
+          <a:off x="16654680" y="928440"/>
+          <a:ext cx="2135880" cy="279000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4518,7 +4518,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="27" t="str">
         <f aca="false">Neu!B4</f>
         <v>B4</v>
@@ -5022,7 +5022,7 @@
       <c r="KP4" s="36"/>
       <c r="KQ4" s="32"/>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="n">
         <f aca="false">Neu!B5</f>
         <v>0</v>
@@ -5330,7 +5330,7 @@
       <c r="KP5" s="38"/>
       <c r="KQ5" s="30"/>
     </row>
-    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="n">
         <f aca="false">Neu!B6</f>
         <v>0</v>
@@ -5638,7 +5638,7 @@
       <c r="KP6" s="38"/>
       <c r="KQ6" s="30"/>
     </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="n">
         <f aca="false">Neu!B7</f>
         <v>0</v>
@@ -5946,7 +5946,7 @@
       <c r="KP7" s="38"/>
       <c r="KQ7" s="30"/>
     </row>
-    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="n">
         <f aca="false">Neu!B8</f>
         <v>0</v>
@@ -6254,7 +6254,7 @@
       <c r="KP8" s="38"/>
       <c r="KQ8" s="30"/>
     </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="n">
         <f aca="false">Neu!B9</f>
         <v>0</v>
@@ -6562,7 +6562,7 @@
       <c r="KP9" s="38"/>
       <c r="KQ9" s="30"/>
     </row>
-    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="n">
         <f aca="false">Neu!B10</f>
         <v>0</v>
@@ -6870,7 +6870,7 @@
       <c r="KP10" s="38"/>
       <c r="KQ10" s="30"/>
     </row>
-    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="n">
         <f aca="false">Neu!B11</f>
         <v>0</v>
@@ -7178,7 +7178,7 @@
       <c r="KP11" s="38"/>
       <c r="KQ11" s="30"/>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="n">
         <f aca="false">Neu!B12</f>
         <v>0</v>
@@ -7486,7 +7486,7 @@
       <c r="KP12" s="38"/>
       <c r="KQ12" s="30"/>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="n">
         <f aca="false">Neu!B13</f>
         <v>0</v>
@@ -7794,7 +7794,7 @@
       <c r="KP13" s="38"/>
       <c r="KQ13" s="30"/>
     </row>
-    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="n">
         <f aca="false">Neu!B14</f>
         <v>0</v>
@@ -8102,7 +8102,7 @@
       <c r="KP14" s="38"/>
       <c r="KQ14" s="30"/>
     </row>
-    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="n">
         <f aca="false">Neu!B15</f>
         <v>0</v>
@@ -8410,7 +8410,7 @@
       <c r="KP15" s="38"/>
       <c r="KQ15" s="30"/>
     </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="n">
         <f aca="false">Neu!B16</f>
         <v>0</v>
@@ -8718,7 +8718,7 @@
       <c r="KP16" s="38"/>
       <c r="KQ16" s="30"/>
     </row>
-    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="n">
         <f aca="false">Neu!B17</f>
         <v>0</v>
@@ -9026,7 +9026,7 @@
       <c r="KP17" s="38"/>
       <c r="KQ17" s="30"/>
     </row>
-    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="n">
         <f aca="false">Neu!B18</f>
         <v>0</v>
@@ -9334,7 +9334,7 @@
       <c r="KP18" s="38"/>
       <c r="KQ18" s="30"/>
     </row>
-    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="n">
         <f aca="false">Neu!B19</f>
         <v>0</v>
@@ -9642,7 +9642,7 @@
       <c r="KP19" s="38"/>
       <c r="KQ19" s="30"/>
     </row>
-    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="n">
         <f aca="false">Neu!B20</f>
         <v>0</v>
@@ -9950,7 +9950,7 @@
       <c r="KP20" s="38"/>
       <c r="KQ20" s="30"/>
     </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="n">
         <f aca="false">Neu!B21</f>
         <v>0</v>
@@ -10258,7 +10258,7 @@
       <c r="KP21" s="38"/>
       <c r="KQ21" s="30"/>
     </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="n">
         <f aca="false">Neu!B22</f>
         <v>0</v>
@@ -10566,7 +10566,7 @@
       <c r="KP22" s="38"/>
       <c r="KQ22" s="30"/>
     </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="n">
         <f aca="false">Neu!B23</f>
         <v>0</v>
@@ -10874,7 +10874,7 @@
       <c r="KP23" s="38"/>
       <c r="KQ23" s="30"/>
     </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="n">
         <f aca="false">Neu!B24</f>
         <v>0</v>
@@ -11770,7 +11770,7 @@
       <c r="DV30" s="45"/>
       <c r="HO30" s="45"/>
     </row>
-    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D31" s="52" t="str">
         <f aca="false">Neu!$B4</f>
         <v>B4</v>
@@ -11888,7 +11888,7 @@
       <c r="DV31" s="45"/>
       <c r="HO31" s="45"/>
     </row>
-    <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D32" s="55" t="n">
         <f aca="false">Neu!$B5</f>
         <v>0</v>
@@ -11963,7 +11963,7 @@
       <c r="DU32" s="45"/>
       <c r="DV32" s="45"/>
     </row>
-    <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D33" s="55" t="n">
         <f aca="false">Neu!$B6</f>
         <v>0</v>
@@ -12038,7 +12038,7 @@
       <c r="DU33" s="45"/>
       <c r="DV33" s="45"/>
     </row>
-    <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D34" s="55" t="n">
         <f aca="false">Neu!$B7</f>
         <v>0</v>
@@ -12104,7 +12104,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D35" s="55" t="n">
         <f aca="false">Neu!$B8</f>
         <v>0</v>
@@ -12170,7 +12170,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D36" s="55" t="n">
         <f aca="false">Neu!$B9</f>
         <v>0</v>
@@ -12236,7 +12236,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D37" s="55" t="n">
         <f aca="false">Neu!$B10</f>
         <v>0</v>
@@ -12302,7 +12302,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D38" s="55" t="n">
         <f aca="false">Neu!$B11</f>
         <v>0</v>
@@ -12368,7 +12368,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D39" s="55" t="n">
         <f aca="false">Neu!$B12</f>
         <v>0</v>
@@ -12434,7 +12434,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D40" s="55" t="n">
         <f aca="false">Neu!$B13</f>
         <v>0</v>
@@ -12500,7 +12500,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D41" s="55" t="n">
         <f aca="false">Neu!$B14</f>
         <v>0</v>
@@ -12566,7 +12566,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D42" s="55" t="n">
         <f aca="false">Neu!$B15</f>
         <v>0</v>
@@ -12632,7 +12632,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D43" s="55" t="n">
         <f aca="false">Neu!$B16</f>
         <v>0</v>
@@ -12698,7 +12698,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D44" s="55" t="n">
         <f aca="false">Neu!$B17</f>
         <v>0</v>
@@ -12764,7 +12764,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D45" s="55" t="n">
         <f aca="false">Neu!$B18</f>
         <v>0</v>
@@ -12830,7 +12830,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D46" s="55" t="n">
         <f aca="false">Neu!$B19</f>
         <v>0</v>
@@ -12896,7 +12896,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D47" s="55" t="n">
         <f aca="false">Neu!$B20</f>
         <v>0</v>
@@ -12962,7 +12962,7 @@
         <v>-60</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D48" s="55" t="n">
         <f aca="false">Neu!$B21</f>
         <v>0</v>
@@ -13026,7 +13026,7 @@
       </c>
       <c r="BE48" s="53"/>
     </row>
-    <row r="49" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D49" s="55" t="n">
         <f aca="false">Neu!$B22</f>
         <v>0</v>
@@ -13090,7 +13090,7 @@
       </c>
       <c r="BE49" s="53"/>
     </row>
-    <row r="50" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D50" s="55" t="n">
         <f aca="false">Neu!$B23</f>
         <v>0</v>
@@ -13154,7 +13154,7 @@
       </c>
       <c r="BE50" s="53"/>
     </row>
-    <row r="51" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D51" s="56" t="n">
         <f aca="false">Neu!$B24</f>
         <v>0</v>
@@ -13646,7 +13646,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="65" t="s">
         <v>92</v>
       </c>
@@ -15205,7 +15205,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="65" t="s">
         <v>92</v>
       </c>
@@ -16699,7 +16699,7 @@
       <c r="V1" s="87"/>
       <c r="W1" s="87"/>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="86"/>
       <c r="B2" s="86"/>
       <c r="C2" s="88" t="str">
@@ -19344,7 +19344,7 @@
       <c r="V1" s="87"/>
       <c r="W1" s="87"/>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="86"/>
       <c r="B2" s="86"/>
       <c r="C2" s="88" t="str">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="AJ1" s="138"/>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="86"/>
       <c r="B2" s="86"/>
       <c r="C2" s="88" t="str">
@@ -24798,7 +24798,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{325E6946-F7D6-4140-816E-E158AC147CBB}</x14:id>
+          <x14:id>{B96500E0-8CF0-4CA0-8684-239456D01C2A}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -24849,7 +24849,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{325E6946-F7D6-4140-816E-E158AC147CBB}">
+          <x14:cfRule type="dataBar" id="{B96500E0-8CF0-4CA0-8684-239456D01C2A}">
             <x14:dataBar minLength="10" maxLength="90" axisPosition="automatic" gradient="false">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -24901,7 +24901,7 @@
       <c r="P1" s="150"/>
       <c r="Q1" s="150"/>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="149"/>
       <c r="B2" s="149"/>
       <c r="C2" s="151" t="str">
